--- a/produits/preuves/sortie/c7-paie-plafond/c7-paie-plafond.xlsx
+++ b/produits/preuves/sortie/c7-paie-plafond/c7-paie-plafond.xlsx
@@ -258,6 +258,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
